--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.41.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.41.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0041.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0041.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,19 +605,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: å¹•</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+5E55 CJK UNIFIED IDEOGRAPH-5E55 | isolated marker/symbol line :: 幕</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: to these â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]Affidavi</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]Affidavi</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: 3</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+5E55 CJK UNIFIED IDEOGRAPH-5E55 | isolated marker/symbol line :: 幕</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -634,7 +638,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "3aof CODY" :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "3aof CODY" :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -665,26 +669,30 @@
       <c r="F3" s="1" t="inlineStr"/>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "3aof CODY" :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "3aof CODY" :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "3aof CODY" :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "3aof CODY" :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: may order that the Subp Ã¦ na to appear to and</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr"/>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to these €</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: ,</t>
+          <t>L23: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr"/>
@@ -727,7 +735,7 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: place or country within which the Subp Ã¦ na is to be</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr"/>
@@ -735,7 +743,7 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L56: symbol-only separator/garbage line :: 1850.</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -758,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,17 +780,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served) after service of the Subp Ã¦ na, within which</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: A</t>
+          <t>L29: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -819,17 +823,13 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: 3. At the time when such Subp Ã¦ na shall be served,</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 8</t>
+          <t>L56: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -866,15 +866,15 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: such Defendant was duly served with the Subp Ã¦ ena,</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr"/>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
@@ -913,7 +913,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L101: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
@@ -952,7 +956,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L103: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
@@ -973,12 +981,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1017,7 +1025,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1051,7 +1059,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
